--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3684-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3684-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F9989E6-AB66-48DF-BF6D-939944AA5DB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0414F795-0859-4473-B70C-3C0473DBF0DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{86C43F84-0AC3-4E8E-BA06-959258AD5916}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{08E8CE3C-FCDD-4403-86E1-33773CAAEB29}"/>
   </bookViews>
   <sheets>
     <sheet name="3684-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1496,29 +1496,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE9B38F2-E07C-4FC4-8CA8-4CC7515A749B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{564BF7CA-5CA4-465C-8DB3-F7AA66450BA1}">
   <dimension ref="A1:X23"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="6.25" customWidth="1"/>
-    <col min="7" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1552,7 +1551,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1588,7 +1587,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1640,7 +1639,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1708,7 +1707,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1780,7 +1779,7 @@
         <v>5.38</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2024</v>
       </c>
@@ -1852,7 +1851,7 @@
         <v>5.75</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2023</v>
       </c>
@@ -1924,7 +1923,7 @@
         <v>1.9</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2022</v>
       </c>
@@ -1996,7 +1995,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="42"/>
       <c r="B9" s="43"/>
       <c r="C9" s="18" t="s">
@@ -2024,7 +2023,7 @@
       <c r="W9" s="49"/>
       <c r="X9" s="45"/>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2021</v>
       </c>
@@ -2096,7 +2095,7 @@
         <v>7.23</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2020</v>
       </c>
@@ -2168,7 +2167,7 @@
         <v>4.5199999999999996</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="36">
         <v>2019</v>
       </c>
@@ -2240,7 +2239,7 @@
         <v>7.89</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2018</v>
       </c>
@@ -2312,7 +2311,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2017</v>
       </c>
@@ -2384,7 +2383,7 @@
         <v>9.66</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2016</v>
       </c>
@@ -2456,7 +2455,7 @@
         <v>8.16</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2015</v>
       </c>
@@ -2528,7 +2527,7 @@
         <v>13.1</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2014</v>
       </c>
@@ -2600,7 +2599,7 @@
         <v>6.52</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="36">
         <v>2013</v>
       </c>
@@ -2672,7 +2671,7 @@
         <v>5.41</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2012</v>
       </c>
@@ -2744,7 +2743,7 @@
         <v>12.1</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="36">
         <v>2011</v>
       </c>
@@ -2816,7 +2815,7 @@
         <v>10.4</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="38">
         <v>2010</v>
       </c>
@@ -2888,7 +2887,7 @@
         <v>6.61</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2009</v>
       </c>
@@ -2960,7 +2959,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="38" t="s">
         <v>45</v>
       </c>
